--- a/资源/UE5Res/Config/jianhuan_newbie.xlsx
+++ b/资源/UE5Res/Config/jianhuan_newbie.xlsx
@@ -1,20 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="13120"/>
+    <workbookView windowWidth="21720" windowHeight="12240"/>
   </bookViews>
   <sheets>
     <sheet name="jianhuan_newbie" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+  <si>
+    <t>RowName</t>
+  </si>
   <si>
     <t>index</t>
   </si>
@@ -67,7 +83,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1217,111 +1233,150 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultColWidth="10.3846153846154" defaultRowHeight="16.8" outlineLevelCol="1"/>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultColWidth="10.3833333333333" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
+    <row r="2" s="1" customFormat="1" spans="1:3">
+      <c r="A2" s="1">
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
+    <row r="3" s="1" customFormat="1" spans="1:3">
+      <c r="A3" s="1">
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
+    <row r="4" spans="1:3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="10" spans="1:3">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="11" spans="1:3">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="13" spans="1:3">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13">
+      <c r="B13">
         <v>10</v>
       </c>
-      <c r="B13" t="s">
-        <v>15</v>
+      <c r="C13" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
